--- a/BA-2026-LG-7740_SharePoint_Deviation_Matrix.xlsx
+++ b/BA-2026-LG-7740_SharePoint_Deviation_Matrix.xlsx
@@ -709,7 +709,7 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>2026-10-20T23:15:27Z</t>
+          <t>2026-10-22T00:15:42Z</t>
         </is>
       </c>
     </row>
